--- a/docs/downloads/08/tbl_produits_elevage_alaotra_tous.xlsx
+++ b/docs/downloads/08/tbl_produits_elevage_alaotra_tous.xlsx
@@ -412,9 +412,6 @@
           <t>Henan'ondry</t>
         </is>
       </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -427,9 +424,6 @@
           <t>Henan-Kisoa</t>
         </is>
       </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -757,9 +751,6 @@
           <t>Vorona</t>
         </is>
       </c>
-      <c r="C27">
-        <v>1</v>
-      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -877,9 +868,6 @@
           <t>Henan'ondry</t>
         </is>
       </c>
-      <c r="C35">
-        <v>1</v>
-      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -952,9 +940,6 @@
           <t>Henan'ondry</t>
         </is>
       </c>
-      <c r="C40">
-        <v>2</v>
-      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -967,9 +952,6 @@
           <t>Henan-Kisoa</t>
         </is>
       </c>
-      <c r="C41">
-        <v>1</v>
-      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -996,9 +978,6 @@
         <is>
           <t>Vorona</t>
         </is>
-      </c>
-      <c r="C43">
-        <v>1</v>
       </c>
     </row>
     <row r="44">

--- a/docs/downloads/08/tbl_produits_elevage_alaotra_tous.xlsx
+++ b/docs/downloads/08/tbl_produits_elevage_alaotra_tous.xlsx
@@ -374,7 +374,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatoharanana</t>
+          <t>Ambatoharanana</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -389,7 +389,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatoharanana</t>
+          <t>Ambatoharanana</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -404,7 +404,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatoharanana</t>
+          <t>Ambatoharanana</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -416,7 +416,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatoharanana</t>
+          <t>Ambatoharanana</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -428,7 +428,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatoharanana</t>
+          <t>Ambatoharanana</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -443,7 +443,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatoharanana</t>
+          <t>Ambatoharanana</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -458,7 +458,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -473,7 +473,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -488,7 +488,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -503,7 +503,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -518,7 +518,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -533,7 +533,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -548,7 +548,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -563,7 +563,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -578,7 +578,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -593,7 +593,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -608,7 +608,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -623,7 +623,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -638,7 +638,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -653,7 +653,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -668,7 +668,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -683,7 +683,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -698,7 +698,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -713,7 +713,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -728,7 +728,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -743,7 +743,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -755,7 +755,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -770,7 +770,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -785,7 +785,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -800,7 +800,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -815,7 +815,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -830,7 +830,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -845,7 +845,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -860,7 +860,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -872,7 +872,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -887,7 +887,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -902,7 +902,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -917,7 +917,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -932,7 +932,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -944,7 +944,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -956,7 +956,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -971,7 +971,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -983,7 +983,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
